--- a/cleaning_pipeline_R/neotree_scripts/zim-scripts/Chinhoyi Maternity Outcome - metadata.xlsx
+++ b/cleaning_pipeline_R/neotree_scripts/zim-scripts/Chinhoyi Maternity Outcome - metadata.xlsx
@@ -1437,10 +1437,10 @@
         <v>form</v>
       </c>
       <c r="F16" t="str">
-        <v>NeoTreeOutcome</v>
+        <v>NeotreeOutcome</v>
       </c>
       <c r="G16" t="str">
-        <v>Outcome</v>
+        <v>Outcome at discharge</v>
       </c>
       <c r="H16" t="str">
         <v>dropdown</v>
